--- a/sample_data/demo_historial_salidas_qy.xlsx
+++ b/sample_data/demo_historial_salidas_qy.xlsx
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="B3" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B4" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B5" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="B6" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
         </is>
       </c>
       <c r="B7" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B8" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B9" s="1" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -637,7 +637,7 @@
         </is>
       </c>
       <c r="B10" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="B11" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B12" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="B13" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="B14" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B15" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B16" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="B17" s="1" t="n">
-        <v>46303</v>
+        <v>46305</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="B18" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         </is>
       </c>
       <c r="B19" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="B20" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B21" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B22" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="B23" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B24" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="B25" s="1" t="n">
-        <v>46302</v>
+        <v>46304</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="B26" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="B27" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         </is>
       </c>
       <c r="B28" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="B29" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B30" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="B31" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="B32" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         </is>
       </c>
       <c r="B33" s="1" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="B34" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="B35" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="B36" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="B37" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B38" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="B39" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="B40" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         </is>
       </c>
       <c r="B41" s="1" t="n">
-        <v>46300</v>
+        <v>46302</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="B42" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="B43" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
         </is>
       </c>
       <c r="B44" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B45" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B46" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="B47" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="B48" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         </is>
       </c>
       <c r="B49" s="1" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="B50" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
         </is>
       </c>
       <c r="B51" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="B52" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="B53" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         </is>
       </c>
       <c r="B54" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B55" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="B56" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="B57" s="1" t="n">
-        <v>46298</v>
+        <v>46300</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="B58" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="B59" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="B60" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         </is>
       </c>
       <c r="B61" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         </is>
       </c>
       <c r="B62" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
         </is>
       </c>
       <c r="B63" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B64" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="B65" s="1" t="n">
-        <v>46297</v>
+        <v>46299</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="B66" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="B67" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="B68" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="B69" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B70" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="B71" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="B72" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B73" s="1" t="n">
-        <v>46296</v>
+        <v>46298</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="B74" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="B75" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B76" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="B77" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         </is>
       </c>
       <c r="B78" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="B79" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="B80" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="B81" s="1" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B82" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="B83" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="B84" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         </is>
       </c>
       <c r="B85" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="B86" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="B87" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
         </is>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="B98" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="B99" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="B100" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         </is>
       </c>
       <c r="B104" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         </is>
       </c>
       <c r="B105" s="1" t="n">
-        <v>46292</v>
+        <v>46294</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="B106" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="B107" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -3121,7 +3121,7 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="B120" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         </is>
       </c>
       <c r="B121" s="1" t="n">
-        <v>46290</v>
+        <v>46292</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="B122" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="B123" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="B124" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="B125" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="B126" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="B127" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="B128" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="B129" s="1" t="n">
-        <v>46289</v>
+        <v>46291</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="B130" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         </is>
       </c>
       <c r="B131" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
         </is>
       </c>
       <c r="B132" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         </is>
       </c>
       <c r="B133" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="B134" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="B135" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         </is>
       </c>
       <c r="B136" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="B137" s="1" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="B138" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -3604,7 +3604,7 @@
         </is>
       </c>
       <c r="B139" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="B140" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -3650,7 +3650,7 @@
         </is>
       </c>
       <c r="B141" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B142" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="B143" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="B144" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         </is>
       </c>
       <c r="B145" s="1" t="n">
-        <v>46287</v>
+        <v>46289</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="B146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="B147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
         </is>
       </c>
       <c r="B148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="B149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="B150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="B151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="B152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         </is>
       </c>
       <c r="B153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="B154" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         </is>
       </c>
       <c r="B155" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="B156" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="B157" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="B158" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         </is>
       </c>
       <c r="B159" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="B160" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="B161" s="1" t="n">
-        <v>46285</v>
+        <v>46287</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         </is>
       </c>
       <c r="B162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="B163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="B164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="B165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="B166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="B167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="B168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         </is>
       </c>
       <c r="B169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="B170" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="B171" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="B172" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         </is>
       </c>
       <c r="B173" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="B174" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         </is>
       </c>
       <c r="B175" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="B176" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="B177" s="1" t="n">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         </is>
       </c>
       <c r="B178" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="B179" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B180" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="B181" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="B182" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="B183" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         </is>
       </c>
       <c r="B184" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="B185" s="1" t="n">
-        <v>46282</v>
+        <v>46284</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="B186" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         </is>
       </c>
       <c r="B187" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B188" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         </is>
       </c>
       <c r="B189" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B190" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
         </is>
       </c>
       <c r="B191" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         </is>
       </c>
       <c r="B192" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B193" s="1" t="n">
-        <v>46281</v>
+        <v>46283</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -4869,7 +4869,7 @@
         </is>
       </c>
       <c r="B194" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         </is>
       </c>
       <c r="B195" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="B196" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="B197" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="B198" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="B199" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         </is>
       </c>
       <c r="B200" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="B201" s="1" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="B202" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         </is>
       </c>
       <c r="B203" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="B204" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="B205" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B206" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="B207" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="B208" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -5214,7 +5214,7 @@
         </is>
       </c>
       <c r="B209" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         </is>
       </c>
       <c r="B210" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="B211" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="B212" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="B213" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         </is>
       </c>
       <c r="B214" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         </is>
       </c>
       <c r="B215" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         </is>
       </c>
       <c r="B216" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="B217" s="1" t="n">
-        <v>46278</v>
+        <v>46280</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="B218" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         </is>
       </c>
       <c r="B219" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         </is>
       </c>
       <c r="B220" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         </is>
       </c>
       <c r="B221" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="B222" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="B223" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="B224" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="B225" s="1" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         </is>
       </c>
       <c r="B226" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="B227" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="B228" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         </is>
       </c>
       <c r="B229" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="B230" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="B231" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         </is>
       </c>
       <c r="B232" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         </is>
       </c>
       <c r="B233" s="1" t="n">
-        <v>46276</v>
+        <v>46278</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="B234" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         </is>
       </c>
       <c r="B235" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="B236" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         </is>
       </c>
       <c r="B237" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="B238" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="B239" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -5927,7 +5927,7 @@
         </is>
       </c>
       <c r="B240" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B241" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
